--- a/Project_ETF/ETF_Investment_Portfolio/0056/ETF_Investment_Portfolio_20260626.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0056/ETF_Investment_Portfolio_20260626.xlsx
@@ -887,17 +887,17 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>2883</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>凱基金</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>575,083,718</t>
+          <t>27,151,304</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
@@ -909,17 +909,17 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2883</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>凱基金</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>27,151,304</t>
+          <t>575,083,718</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
@@ -1063,17 +1063,17 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>2884</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>玉山金</t>
+          <t>遠傳</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>416,745,337</t>
+          <t>134,555,520</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -1085,17 +1085,17 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>2884</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>遠傳</t>
+          <t>玉山金</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>134,555,520</t>
+          <t>416,745,337</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -1613,17 +1613,17 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>2385</t>
+          <t>3023</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>群光</t>
+          <t>信邦</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>33,080,543</t>
+          <t>10,902,665</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -1635,17 +1635,17 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>3023</t>
+          <t>2385</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>信邦</t>
+          <t>群光</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>10,902,665</t>
+          <t>33,080,543</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
